--- a/artfynd/A 61153-2024 artfynd.xlsx
+++ b/artfynd/A 61153-2024 artfynd.xlsx
@@ -1150,7 +1150,7 @@
         <v>122289235</v>
       </c>
       <c r="B6" t="n">
-        <v>78645</v>
+        <v>78646</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 61153-2024 artfynd.xlsx
+++ b/artfynd/A 61153-2024 artfynd.xlsx
@@ -1026,7 +1026,7 @@
         <v>122148271</v>
       </c>
       <c r="B5" t="n">
-        <v>57527</v>
+        <v>57532</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>122289235</v>
       </c>
       <c r="B6" t="n">
-        <v>78646</v>
+        <v>78651</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>122354442</v>
       </c>
       <c r="B7" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 61153-2024 artfynd.xlsx
+++ b/artfynd/A 61153-2024 artfynd.xlsx
@@ -1041,11 +1041,6 @@
       <c r="E5" t="n">
         <v>103021</v>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>Poecile montanus</t>
@@ -1150,7 +1145,7 @@
         <v>122289235</v>
       </c>
       <c r="B6" t="n">
-        <v>78651</v>
+        <v>78652</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,11 +1159,6 @@
       </c>
       <c r="E6" t="n">
         <v>6425</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1270,11 +1260,6 @@
       </c>
       <c r="E7" t="n">
         <v>100049</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>

--- a/artfynd/A 61153-2024 artfynd.xlsx
+++ b/artfynd/A 61153-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1026,7 +1026,7 @@
         <v>122148271</v>
       </c>
       <c r="B5" t="n">
-        <v>57532</v>
+        <v>57536</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1040,6 +1040,11 @@
       </c>
       <c r="E5" t="n">
         <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1145,7 +1150,7 @@
         <v>122289235</v>
       </c>
       <c r="B6" t="n">
-        <v>78652</v>
+        <v>78656</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,6 +1164,11 @@
       </c>
       <c r="E6" t="n">
         <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1246,7 +1256,7 @@
         <v>122354442</v>
       </c>
       <c r="B7" t="n">
-        <v>57395</v>
+        <v>57399</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,6 +1270,11 @@
       </c>
       <c r="E7" t="n">
         <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1349,6 +1364,131 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>122550912</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56593</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>O Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>476054</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7008562</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färsk spillning och tjädertallar som de nyilgen ätit på.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen, Thomas Holmberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61153-2024 artfynd.xlsx
+++ b/artfynd/A 61153-2024 artfynd.xlsx
@@ -1253,10 +1253,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122354442</v>
+        <v>122550912</v>
       </c>
       <c r="B7" t="n">
-        <v>57399</v>
+        <v>56593</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,37 +1265,33 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>permanent revir</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1305,13 +1301,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>475969</v>
+        <v>476054</v>
       </c>
       <c r="R7" t="n">
-        <v>7008530</v>
+        <v>7008562</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1335,12 +1331,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-01-19</t>
+          <t>2025-02-10</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Färsk spillning och tjädertallar som de nyilgen ätit på.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,52 +1371,56 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Ulla Falkdalen</t>
+          <t>Ulla Falkdalen, Thomas Holmberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122550912</v>
+        <v>122354442</v>
       </c>
       <c r="B8" t="n">
-        <v>56593</v>
+        <v>57399</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>permanent revir</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1415,13 +1430,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476054</v>
+        <v>475969</v>
       </c>
       <c r="R8" t="n">
-        <v>7008562</v>
+        <v>7008530</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1445,27 +1460,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:30</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-02-10</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färsk spillning och tjädertallar som de nyilgen ätit på.</t>
+          <t>2025-01-19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ulla Falkdalen, Thomas Holmberg</t>
+          <t>Ulla Falkdalen</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>

--- a/artfynd/A 61153-2024 artfynd.xlsx
+++ b/artfynd/A 61153-2024 artfynd.xlsx
@@ -1150,7 +1150,7 @@
         <v>122289235</v>
       </c>
       <c r="B6" t="n">
-        <v>78656</v>
+        <v>78657</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>122550912</v>
       </c>
       <c r="B7" t="n">
-        <v>56593</v>
+        <v>56594</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1381,7 +1381,7 @@
         <v>122354442</v>
       </c>
       <c r="B8" t="n">
-        <v>57399</v>
+        <v>57400</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 61153-2024 artfynd.xlsx
+++ b/artfynd/A 61153-2024 artfynd.xlsx
@@ -1150,7 +1150,7 @@
         <v>122289235</v>
       </c>
       <c r="B6" t="n">
-        <v>78657</v>
+        <v>78660</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 61153-2024 artfynd.xlsx
+++ b/artfynd/A 61153-2024 artfynd.xlsx
@@ -1495,7 +1495,7 @@
         <v>122776844</v>
       </c>
       <c r="B9" t="n">
-        <v>57631</v>
+        <v>57634</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 61153-2024 artfynd.xlsx
+++ b/artfynd/A 61153-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1614,6 +1614,260 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123826591</v>
+      </c>
+      <c r="B10" t="n">
+        <v>56697</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>476180</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7008550</v>
+      </c>
+      <c r="S10" t="n">
+        <v>14</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>En färsk spillningshög</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123826657</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57493</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>O Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>476054</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7008562</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-04-05</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Även sedd i Tannetorpen nyligen av boende.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ulla Falkdalen</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61153-2024 artfynd.xlsx
+++ b/artfynd/A 61153-2024 artfynd.xlsx
@@ -1616,10 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123826591</v>
+        <v>123826657</v>
       </c>
       <c r="B10" t="n">
-        <v>56697</v>
+        <v>57496</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1628,49 +1628,53 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100048</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Storflon, Jmt</t>
+          <t>O Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476180</v>
+        <v>476054</v>
       </c>
       <c r="R10" t="n">
-        <v>7008550</v>
+        <v>7008562</v>
       </c>
       <c r="S10" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1694,7 +1698,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1704,7 +1708,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -1714,7 +1718,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>En färsk spillningshög</t>
+          <t>Även sedd i Tannetorpen nyligen av boende.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1741,10 +1745,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123826657</v>
+        <v>123826591</v>
       </c>
       <c r="B11" t="n">
-        <v>57493</v>
+        <v>56700</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1753,53 +1757,49 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100048</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>O Storflon, Jmt</t>
+          <t>Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476054</v>
+        <v>476180</v>
       </c>
       <c r="R11" t="n">
-        <v>7008562</v>
+        <v>7008550</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-04-05</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-04-05</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Även sedd i Tannetorpen nyligen av boende.</t>
+          <t>En färsk spillningshög</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 61153-2024 artfynd.xlsx
+++ b/artfynd/A 61153-2024 artfynd.xlsx
@@ -1619,7 +1619,7 @@
         <v>123826657</v>
       </c>
       <c r="B10" t="n">
-        <v>57496</v>
+        <v>57497</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 61153-2024 artfynd.xlsx
+++ b/artfynd/A 61153-2024 artfynd.xlsx
@@ -1616,10 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123826657</v>
+        <v>123826591</v>
       </c>
       <c r="B10" t="n">
-        <v>57497</v>
+        <v>56700</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1628,53 +1628,49 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100048</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>O Storflon, Jmt</t>
+          <t>Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476054</v>
+        <v>476180</v>
       </c>
       <c r="R10" t="n">
-        <v>7008562</v>
+        <v>7008550</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1698,7 +1694,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-04-05</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1708,7 +1704,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-04-05</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -1718,7 +1714,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Även sedd i Tannetorpen nyligen av boende.</t>
+          <t>En färsk spillningshög</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1745,10 +1741,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123826591</v>
+        <v>123826657</v>
       </c>
       <c r="B11" t="n">
-        <v>56700</v>
+        <v>57497</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1757,49 +1753,53 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>100048</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Storflon, Jmt</t>
+          <t>O Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476180</v>
+        <v>476054</v>
       </c>
       <c r="R11" t="n">
-        <v>7008550</v>
+        <v>7008562</v>
       </c>
       <c r="S11" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>En färsk spillningshög</t>
+          <t>Även sedd i Tannetorpen nyligen av boende.</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 61153-2024 artfynd.xlsx
+++ b/artfynd/A 61153-2024 artfynd.xlsx
@@ -1616,10 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123826591</v>
+        <v>123826657</v>
       </c>
       <c r="B10" t="n">
-        <v>56700</v>
+        <v>57497</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1628,49 +1628,53 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100048</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Storflon, Jmt</t>
+          <t>O Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476180</v>
+        <v>476054</v>
       </c>
       <c r="R10" t="n">
-        <v>7008550</v>
+        <v>7008562</v>
       </c>
       <c r="S10" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1694,7 +1698,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1704,7 +1708,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -1714,7 +1718,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>En färsk spillningshög</t>
+          <t>Även sedd i Tannetorpen nyligen av boende.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1741,10 +1745,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123826657</v>
+        <v>123826591</v>
       </c>
       <c r="B11" t="n">
-        <v>57497</v>
+        <v>56700</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1753,53 +1757,49 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100048</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>O Storflon, Jmt</t>
+          <t>Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476054</v>
+        <v>476180</v>
       </c>
       <c r="R11" t="n">
-        <v>7008562</v>
+        <v>7008550</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-04-05</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-04-05</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Även sedd i Tannetorpen nyligen av boende.</t>
+          <t>En färsk spillningshög</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 61153-2024 artfynd.xlsx
+++ b/artfynd/A 61153-2024 artfynd.xlsx
@@ -1616,10 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123826657</v>
+        <v>123826591</v>
       </c>
       <c r="B10" t="n">
-        <v>57519</v>
+        <v>56722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1628,53 +1628,49 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100048</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>O Storflon, Jmt</t>
+          <t>Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>476054</v>
+        <v>476180</v>
       </c>
       <c r="R10" t="n">
-        <v>7008562</v>
+        <v>7008550</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1698,7 +1694,7 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-04-05</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -1708,7 +1704,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-04-05</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -1718,7 +1714,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Även sedd i Tannetorpen nyligen av boende.</t>
+          <t>En färsk spillningshög</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1745,10 +1741,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123826591</v>
+        <v>123826657</v>
       </c>
       <c r="B11" t="n">
-        <v>56722</v>
+        <v>57519</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1757,49 +1753,53 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>100048</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Storflon, Jmt</t>
+          <t>O Storflon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>476180</v>
+        <v>476054</v>
       </c>
       <c r="R11" t="n">
-        <v>7008550</v>
+        <v>7008562</v>
       </c>
       <c r="S11" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-04-05</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>En färsk spillningshög</t>
+          <t>Även sedd i Tannetorpen nyligen av boende.</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 61153-2024 artfynd.xlsx
+++ b/artfynd/A 61153-2024 artfynd.xlsx
@@ -1748,7 +1748,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">

--- a/artfynd/A 61153-2024 artfynd.xlsx
+++ b/artfynd/A 61153-2024 artfynd.xlsx
@@ -1744,7 +1744,7 @@
         <v>123826657</v>
       </c>
       <c r="B11" t="n">
-        <v>57519</v>
+        <v>57648</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 61153-2024 artfynd.xlsx
+++ b/artfynd/A 61153-2024 artfynd.xlsx
@@ -1746,11 +1746,6 @@
       <c r="B11" t="n">
         <v>57648</v>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>NT</t>

--- a/artfynd/A 61153-2024 artfynd.xlsx
+++ b/artfynd/A 61153-2024 artfynd.xlsx
@@ -1381,12 +1381,7 @@
         <v>122354442</v>
       </c>
       <c r="B8" t="n">
-        <v>57494</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57861</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
